--- a/templates/거래명세서_template.xlsx
+++ b/templates/거래명세서_template.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAILYCIGAR_DB\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257F4F1F-FD13-42AA-8ABB-E6D9A223AE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232FBA1B-300A-48A5-B5BC-4218EF696AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="14892" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="거래명세서" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">거래명세서!$A$1:$K$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">거래명세서!$A$1:$K$61</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>거 래 명 세 서</t>
   </si>
@@ -96,14 +96,6 @@
   </si>
   <si>
     <t>비고를 입력해주세요.</t>
-  </si>
-  <si>
-    <t>DON JUAN URQUIJO 20° ANIVERSARIO - ROBUSTO</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>DON JUAN URQUIJO 20° ANIVERSARIO - CORONAS</t>
-    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>㈜ 데일리시가</t>
@@ -119,74 +111,6 @@
   </si>
   <si>
     <t>㈜데일리시가</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flor Fina – Cigarillo (Puritos)</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flor Fina – Cigarillo (Chocolate)</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flor Fina – Cigarillo (Caramel)</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flor Fina – Cigarillo (Café Crème)</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flor Fina – Cigarillo (Vanilla)</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>TABACALERA - HALF CORONAS</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>TABACALERA - ROBUSTO</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALHAMBRA - CORONAS</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALHAMBRA - ROBUSTO</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>DON JUAN URQUIJO 20° ANIVERSARIO - TORO</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>DON JUAN URQUIJO VINTAGE BLEND – CORONAS</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>TABACALERA EDICION MADURO – CORONAS</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>TABACALERA EDICION MADURO – ROBUSTO</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>1881 - CORONAS</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>1881 PERIQUE MADURO - SHORT ROBUSTO</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>1881 PERIQUE BOLD MADURO - SHORT ROBUSTO</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>TABACALERA GRAN RESERVA - ROBUSTO</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
@@ -823,107 +747,107 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1024,13 +948,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>281940</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>601980</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1299,7 +1223,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J48"/>
+  <dimension ref="B1:J60"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="1.6640625" customWidth="1"/>
@@ -1317,45 +1241,45 @@
   <sheetData>
     <row r="1" spans="2:10" ht="6" customHeight="1"/>
     <row r="2" spans="2:10" ht="36" customHeight="1">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="I2" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="39"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="I2" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="26"/>
     </row>
     <row r="3" spans="2:10" ht="15.6">
       <c r="B3" s="15"/>
       <c r="C3" s="16" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D3" s="15"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
     </row>
     <row r="4" spans="2:10" ht="13.5" customHeight="1">
-      <c r="C4" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="C4" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
       <c r="I4" s="17"/>
       <c r="J4" s="14"/>
     </row>
     <row r="5" spans="2:10" ht="13.5" customHeight="1">
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
       <c r="I5" s="17"/>
       <c r="J5" s="14"/>
     </row>
     <row r="6" spans="2:10" ht="13.5" customHeight="1">
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
     </row>
     <row r="7" spans="2:10" ht="13.5" customHeight="1">
       <c r="B7" s="1"/>
@@ -1371,11 +1295,11 @@
     <row r="8" spans="2:10" ht="9.75" customHeight="1"/>
     <row r="9" spans="2:10" ht="4.5" customHeight="1"/>
     <row r="10" spans="2:10" ht="18" customHeight="1">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
       <c r="E10" s="52" t="s">
         <v>2</v>
       </c>
@@ -1390,63 +1314,63 @@
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="36">
         <v>20260314001</v>
       </c>
-      <c r="D12" s="49"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
+      <c r="H12" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
     </row>
     <row r="13" spans="2:10" ht="18" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="35">
         <v>46095</v>
       </c>
-      <c r="D13" s="49"/>
+      <c r="D13" s="36"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
+      <c r="H13" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
     </row>
     <row r="14" spans="2:10" ht="18" customHeight="1">
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="35">
         <v>46098</v>
       </c>
-      <c r="D14" s="49"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
+      <c r="H14" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" spans="2:10" ht="18" customHeight="1" thickBot="1">
       <c r="B15" s="3"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1456,12 +1380,12 @@
     </row>
     <row r="16" spans="2:10" ht="18" customHeight="1" thickBot="1"/>
     <row r="17" spans="2:10" ht="18" customHeight="1" thickBot="1">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="44"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="4" t="s">
         <v>10</v>
       </c>
@@ -1479,598 +1403,482 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="18" customHeight="1">
-      <c r="B18" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="6">
-        <v>23000</v>
-      </c>
-      <c r="G18" s="6">
-        <v>2</v>
-      </c>
-      <c r="H18" s="6">
-        <f t="shared" ref="H18:H19" si="0">IF(AND(F18=0,G18=0),0,F18*G18)</f>
-        <v>46000</v>
-      </c>
-      <c r="I18" s="6">
-        <f t="shared" ref="I18:I36" si="1">ROUND(H18*0.1,0)</f>
-        <v>4600</v>
-      </c>
-      <c r="J18" s="7">
-        <f t="shared" ref="J18:J36" si="2">H18+I18</f>
-        <v>50600</v>
-      </c>
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="2:10" ht="18" customHeight="1">
-      <c r="B19" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="8">
-        <v>23000</v>
-      </c>
-      <c r="G19" s="8">
-        <v>2</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="0"/>
-        <v>46000</v>
-      </c>
-      <c r="I19" s="8">
-        <f t="shared" si="1"/>
-        <v>4600</v>
-      </c>
-      <c r="J19" s="9">
-        <f t="shared" si="2"/>
-        <v>50600</v>
-      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="20" spans="2:10" ht="18" customHeight="1">
-      <c r="B20" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="6">
-        <v>23000</v>
-      </c>
-      <c r="G20" s="6">
-        <v>2</v>
-      </c>
-      <c r="H20" s="6">
-        <f t="shared" ref="H20:H21" si="3">IF(AND(F20=0,G20=0),0,F20*G20)</f>
-        <v>46000</v>
-      </c>
-      <c r="I20" s="6">
-        <f t="shared" si="1"/>
-        <v>4600</v>
-      </c>
-      <c r="J20" s="7">
-        <f t="shared" si="2"/>
-        <v>50600</v>
-      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="7"/>
     </row>
     <row r="21" spans="2:10" ht="18" customHeight="1">
-      <c r="B21" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="8">
-        <v>23000</v>
-      </c>
-      <c r="G21" s="8">
-        <v>2</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="3"/>
-        <v>46000</v>
-      </c>
-      <c r="I21" s="8">
-        <f t="shared" si="1"/>
-        <v>4600</v>
-      </c>
-      <c r="J21" s="9">
-        <f t="shared" si="2"/>
-        <v>50600</v>
-      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="9"/>
     </row>
     <row r="22" spans="2:10" ht="18" customHeight="1">
-      <c r="B22" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="6">
-        <v>23000</v>
-      </c>
-      <c r="G22" s="6">
-        <v>2</v>
-      </c>
-      <c r="H22" s="6">
-        <f t="shared" ref="H22:H36" si="4">IF(AND(F22=0,G22=0),0,F22*G22)</f>
-        <v>46000</v>
-      </c>
-      <c r="I22" s="6">
-        <f t="shared" si="1"/>
-        <v>4600</v>
-      </c>
-      <c r="J22" s="7">
-        <f t="shared" si="2"/>
-        <v>50600</v>
-      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" spans="2:10" ht="18" customHeight="1">
-      <c r="B23" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="8">
-        <v>9000</v>
-      </c>
-      <c r="G23" s="8">
-        <v>5</v>
-      </c>
-      <c r="H23" s="8">
-        <f t="shared" si="4"/>
-        <v>45000</v>
-      </c>
-      <c r="I23" s="8">
-        <f t="shared" si="1"/>
-        <v>4500</v>
-      </c>
-      <c r="J23" s="9">
-        <f t="shared" si="2"/>
-        <v>49500</v>
-      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="9"/>
     </row>
     <row r="24" spans="2:10" ht="18" customHeight="1">
-      <c r="B24" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="6">
-        <v>13000</v>
-      </c>
-      <c r="G24" s="6">
-        <v>5</v>
-      </c>
-      <c r="H24" s="6">
-        <f t="shared" si="4"/>
-        <v>65000</v>
-      </c>
-      <c r="I24" s="6">
-        <f t="shared" si="1"/>
-        <v>6500</v>
-      </c>
-      <c r="J24" s="7">
-        <f t="shared" si="2"/>
-        <v>71500</v>
-      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" spans="2:10" ht="18" customHeight="1">
-      <c r="B25" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="8">
-        <v>14000</v>
-      </c>
-      <c r="G25" s="8">
-        <v>5</v>
-      </c>
-      <c r="H25" s="8">
-        <f t="shared" si="4"/>
-        <v>70000</v>
-      </c>
-      <c r="I25" s="8">
-        <f t="shared" si="1"/>
-        <v>7000</v>
-      </c>
-      <c r="J25" s="9">
-        <f t="shared" si="2"/>
-        <v>77000</v>
-      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="9"/>
     </row>
     <row r="26" spans="2:10" ht="18" customHeight="1">
-      <c r="B26" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="6">
-        <v>15000</v>
-      </c>
-      <c r="G26" s="6">
-        <v>5</v>
-      </c>
-      <c r="H26" s="6">
-        <f t="shared" si="4"/>
-        <v>75000</v>
-      </c>
-      <c r="I26" s="6">
-        <f t="shared" si="1"/>
-        <v>7500</v>
-      </c>
-      <c r="J26" s="7">
-        <f t="shared" si="2"/>
-        <v>82500</v>
-      </c>
+      <c r="B26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="7"/>
     </row>
     <row r="27" spans="2:10" ht="18" customHeight="1">
-      <c r="B27" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="8">
-        <v>16000</v>
-      </c>
-      <c r="G27" s="8">
-        <v>5</v>
-      </c>
-      <c r="H27" s="8">
-        <f t="shared" si="4"/>
-        <v>80000</v>
-      </c>
-      <c r="I27" s="8">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-      <c r="J27" s="9">
-        <f t="shared" si="2"/>
-        <v>88000</v>
-      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="9"/>
     </row>
     <row r="28" spans="2:10" ht="18" customHeight="1">
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="7"/>
+    </row>
+    <row r="29" spans="2:10" ht="18" customHeight="1">
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="9"/>
+    </row>
+    <row r="30" spans="2:10" ht="18" customHeight="1">
+      <c r="B30" s="18"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="7"/>
+    </row>
+    <row r="31" spans="2:10" ht="18" customHeight="1">
+      <c r="B31" s="21"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="9"/>
+    </row>
+    <row r="32" spans="2:10" ht="18" customHeight="1">
+      <c r="B32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="7"/>
+    </row>
+    <row r="33" spans="2:10" ht="18" customHeight="1">
+      <c r="B33" s="21"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="9"/>
+    </row>
+    <row r="34" spans="2:10" ht="18" customHeight="1">
+      <c r="B34" s="18"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="7"/>
+    </row>
+    <row r="35" spans="2:10" ht="18" customHeight="1">
+      <c r="B35" s="21"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="9"/>
+    </row>
+    <row r="36" spans="2:10" ht="18" customHeight="1">
+      <c r="B36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="7"/>
+    </row>
+    <row r="37" spans="2:10" ht="18" customHeight="1">
+      <c r="B37" s="21"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="9"/>
+    </row>
+    <row r="38" spans="2:10" ht="18" customHeight="1">
+      <c r="B38" s="18"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="7"/>
+    </row>
+    <row r="39" spans="2:10" ht="18" customHeight="1">
+      <c r="B39" s="21"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="9"/>
+    </row>
+    <row r="40" spans="2:10" ht="18" customHeight="1">
+      <c r="B40" s="18"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="7"/>
+    </row>
+    <row r="41" spans="2:10" ht="18" customHeight="1">
+      <c r="B41" s="21"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="9"/>
+    </row>
+    <row r="42" spans="2:10" ht="18" customHeight="1">
+      <c r="B42" s="18"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="7"/>
+    </row>
+    <row r="43" spans="2:10" ht="18" customHeight="1">
+      <c r="B43" s="21"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="9"/>
+    </row>
+    <row r="44" spans="2:10" ht="18" customHeight="1">
+      <c r="B44" s="18"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="7"/>
+    </row>
+    <row r="45" spans="2:10" ht="18" customHeight="1">
+      <c r="B45" s="21"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="9"/>
+    </row>
+    <row r="46" spans="2:10" ht="18" customHeight="1">
+      <c r="B46" s="18"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="7"/>
+    </row>
+    <row r="47" spans="2:10" ht="18" customHeight="1">
+      <c r="B47" s="21"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="9"/>
+    </row>
+    <row r="48" spans="2:10" ht="18" customHeight="1">
+      <c r="B48" s="44"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="9"/>
+    </row>
+    <row r="49" spans="2:10" ht="18" customHeight="1" thickBot="1">
+      <c r="B49" s="47"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="51" spans="2:10" ht="18" customHeight="1">
+      <c r="E51" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="41">
+        <f>SUM(H18:H49)</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="41"/>
+    </row>
+    <row r="52" spans="2:10" ht="18" customHeight="1">
+      <c r="E52" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="41">
+        <f>SUM(I18:I49)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="41"/>
+    </row>
+    <row r="53" spans="2:10" ht="18" customHeight="1">
+      <c r="E53" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="42">
+        <f>I51+I52</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="42"/>
+    </row>
+    <row r="54" spans="2:10" ht="6" customHeight="1"/>
+    <row r="55" spans="2:10" ht="13.5" customHeight="1">
+      <c r="B55" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="39"/>
+      <c r="D55" s="39"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
+      <c r="J55" s="39"/>
+    </row>
+    <row r="56" spans="2:10" ht="45" customHeight="1">
+      <c r="B56" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="43"/>
+      <c r="J56" s="43"/>
+    </row>
+    <row r="57" spans="2:10" ht="7.5" customHeight="1"/>
+    <row r="58" spans="2:10" ht="9.75" customHeight="1"/>
+    <row r="59" spans="2:10" ht="49.5" customHeight="1">
+      <c r="B59" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="6">
-        <v>21000</v>
-      </c>
-      <c r="G28" s="6">
-        <v>5</v>
-      </c>
-      <c r="H28" s="6">
-        <f t="shared" si="4"/>
-        <v>105000</v>
-      </c>
-      <c r="I28" s="6">
-        <f t="shared" si="1"/>
-        <v>10500</v>
-      </c>
-      <c r="J28" s="7">
-        <f t="shared" si="2"/>
-        <v>115500</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" ht="18" customHeight="1">
-      <c r="B29" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="8">
-        <v>29000</v>
-      </c>
-      <c r="G29" s="8">
-        <v>5</v>
-      </c>
-      <c r="H29" s="8">
-        <f t="shared" si="4"/>
-        <v>145000</v>
-      </c>
-      <c r="I29" s="8">
-        <f t="shared" si="1"/>
-        <v>14500</v>
-      </c>
-      <c r="J29" s="9">
-        <f t="shared" si="2"/>
-        <v>159500</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" ht="18" customHeight="1">
-      <c r="B30" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="6">
-        <v>19000</v>
-      </c>
-      <c r="G30" s="6">
-        <v>5</v>
-      </c>
-      <c r="H30" s="6">
-        <f t="shared" si="4"/>
-        <v>95000</v>
-      </c>
-      <c r="I30" s="6">
-        <f t="shared" si="1"/>
-        <v>9500</v>
-      </c>
-      <c r="J30" s="7">
-        <f t="shared" si="2"/>
-        <v>104500</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" ht="18" customHeight="1">
-      <c r="B31" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="8">
-        <v>26000</v>
-      </c>
-      <c r="G31" s="8">
-        <v>5</v>
-      </c>
-      <c r="H31" s="8">
-        <f t="shared" si="4"/>
-        <v>130000</v>
-      </c>
-      <c r="I31" s="8">
-        <f t="shared" si="1"/>
-        <v>13000</v>
-      </c>
-      <c r="J31" s="9">
-        <f t="shared" si="2"/>
-        <v>143000</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" ht="18" customHeight="1">
-      <c r="B32" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="6">
-        <v>30000</v>
-      </c>
-      <c r="G32" s="6">
-        <v>5</v>
-      </c>
-      <c r="H32" s="6">
-        <f t="shared" si="4"/>
-        <v>150000</v>
-      </c>
-      <c r="I32" s="6">
-        <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-      <c r="J32" s="7">
-        <f t="shared" si="2"/>
-        <v>165000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" ht="18" customHeight="1">
-      <c r="B33" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="8">
-        <v>16000</v>
-      </c>
-      <c r="G33" s="8">
-        <v>5</v>
-      </c>
-      <c r="H33" s="8">
-        <f t="shared" si="4"/>
-        <v>80000</v>
-      </c>
-      <c r="I33" s="8">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-      <c r="J33" s="9">
-        <f t="shared" si="2"/>
-        <v>88000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" ht="18" customHeight="1">
-      <c r="B34" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="6">
-        <v>36000</v>
-      </c>
-      <c r="G34" s="6">
-        <v>5</v>
-      </c>
-      <c r="H34" s="6">
-        <f t="shared" si="4"/>
-        <v>180000</v>
-      </c>
-      <c r="I34" s="6">
-        <f t="shared" si="1"/>
-        <v>18000</v>
-      </c>
-      <c r="J34" s="7">
-        <f t="shared" si="2"/>
-        <v>198000</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" ht="18" customHeight="1">
-      <c r="B35" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="8">
-        <v>39000</v>
-      </c>
-      <c r="G35" s="8">
-        <v>5</v>
-      </c>
-      <c r="H35" s="8">
-        <f t="shared" si="4"/>
-        <v>195000</v>
-      </c>
-      <c r="I35" s="8">
-        <f t="shared" si="1"/>
-        <v>19500</v>
-      </c>
-      <c r="J35" s="9">
-        <f t="shared" si="2"/>
-        <v>214500</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" ht="18" customHeight="1">
-      <c r="B36" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="6">
-        <v>48000</v>
-      </c>
-      <c r="G36" s="6">
-        <v>5</v>
-      </c>
-      <c r="H36" s="8">
-        <f t="shared" si="4"/>
-        <v>240000</v>
-      </c>
-      <c r="I36" s="8">
-        <f t="shared" si="1"/>
-        <v>24000</v>
-      </c>
-      <c r="J36" s="9">
-        <f t="shared" si="2"/>
-        <v>264000</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" ht="18" customHeight="1" thickBot="1">
-      <c r="B37" s="34"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" spans="2:10" ht="15.75" customHeight="1"/>
-    <row r="39" spans="2:10" ht="18" customHeight="1">
-      <c r="E39" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="27">
-        <f>SUM(H18:H37)</f>
-        <v>1885000</v>
-      </c>
-      <c r="J39" s="27"/>
-    </row>
-    <row r="40" spans="2:10" ht="18" customHeight="1">
-      <c r="E40" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="27">
-        <f>SUM(I18:I37)</f>
-        <v>188500</v>
-      </c>
-      <c r="J40" s="27"/>
-    </row>
-    <row r="41" spans="2:10" ht="18" customHeight="1">
-      <c r="E41" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="28">
-        <f>I39+I40</f>
-        <v>2073500</v>
-      </c>
-      <c r="J41" s="28"/>
-    </row>
-    <row r="42" spans="2:10" ht="6" customHeight="1"/>
-    <row r="43" spans="2:10" ht="13.5" customHeight="1">
-      <c r="B43" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-    </row>
-    <row r="44" spans="2:10" ht="45" customHeight="1">
-      <c r="B44" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-    </row>
-    <row r="45" spans="2:10" ht="7.5" customHeight="1"/>
-    <row r="46" spans="2:10" ht="9.75" customHeight="1"/>
-    <row r="47" spans="2:10" ht="49.5" customHeight="1">
-      <c r="B47" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-    </row>
-    <row r="48" spans="2:10" ht="7.5" customHeight="1"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="40"/>
+    </row>
+    <row r="60" spans="2:10" ht="7.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="53">
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="C4:E5"/>
     <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B59:J59"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="B55:J55"/>
+    <mergeCell ref="B56:J56"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="B20:E20"/>
@@ -2084,31 +1892,6 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B47:J47"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="B43:J43"/>
-    <mergeCell ref="B44:J44"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="C4:E5"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="H12:J12"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
